--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\3d printing\stormwalker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1491B435-9629-40F9-B3BB-EC819885CD23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1324035C-1E24-4134-A15C-1330E939F374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2268" yWindow="2268" windowWidth="27276" windowHeight="22044" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11520" yWindow="5544" windowWidth="34560" windowHeight="18852" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Body" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="304">
   <si>
     <t>Category</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -159,38 +159,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">3060 extrusion (3mm thickness) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF3399"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Custom ordered)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>3060 extrusion (3mm thickness)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF3399"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Custom ordered)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Steel Plate</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -203,22 +171,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Steel Plate </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF3399"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Custom ordered)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Frame Bracket</t>
   </si>
   <si>
@@ -322,39 +274,919 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Carbon Fiber Sheet</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF3399"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Custom ordered)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Thermister</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>1mm Aluminum PCB</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF3399"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Custom ordered)</t>
-    </r>
+    <t>PEI Sheet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Voron 0 Textured PEI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cooling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cooling Fan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weaker variants would work.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GFC0412DS-SM06</t>
+  </si>
+  <si>
+    <t>Misc.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Endstops</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D2F style microswitch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No lever</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLS-M6-00 (304 stainless steel, thinnest variant)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200g</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pack PET parts tightly in salt and air fry for 2 hours at 130-140C.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T nut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020 M3 Nut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nuts</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020 M5 Nut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Popcorn Salt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Delta 4056 Fan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Integrated Lead Screw Stepper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90 Degree 3030 Corner Bracket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Threaded Heat Insert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dimensions are in hole diameter x outer diameter x height.
+Some vendors use hole diameter x height x outer diameter, check before buying.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self-Clinching Nut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M6x8x10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M6 Threaded Heat Insert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3 Threaded Heat Insert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3x5x10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3 Nut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M4 Nut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M6 Nut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shim</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3 Shim</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3x16x1, stainless steel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10mm~16mm diameter ones would work. Grind the top surface on the extrusion away, and put the sharp side of the shim towards the extrusion to ground the frame.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26AWG</t>
+  </si>
+  <si>
+    <t>26AWG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Silicone wire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20AWG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wire Sleeve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Split Braided Sleeving</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>For wiring thermistors and endstops.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Micro-Fit 3.0 Crimp Terminal, Female</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crimp Terminal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wiring</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Micro-Fit 3.0 Receptacle Housing, Dual Row</t>
+  </si>
+  <si>
+    <t>430252400 (2x12)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wire Housing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>430252000 (2x10)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Uses 43. Buy extra if not confident with wiring.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buy extra if not confident with wiring.</t>
+  </si>
+  <si>
+    <t>Micro-Fit 3.0 Receptacle Housing, Dual Row</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Micro-Fit 3.0 Vertical Header, Dual Row</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>430452412 (2x12)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>430452012 (2x10)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wire Connector</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use expensive ones for Z axis. Can use cheap ones for X and Y.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JST XH Series Straight Through Hole PCB Header</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2 Pin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Screw Terminal Block</t>
+  </si>
+  <si>
+    <t>2pin, 3.5mm pitch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Both top entry and side entry would work.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3 Pin</t>
+  </si>
+  <si>
+    <t>4 Pin</t>
+  </si>
+  <si>
+    <t>425 Glue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>407 Glue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basically plastic-safe threadlocker. Apply on screws after installing.
+Warning: if accidentally went into screw socket, immediately insert screwdriver into socket and wait 30 seconds for it to dry to prevent gluing the socket shut.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30x40x5mm</t>
+  </si>
+  <si>
+    <t>Heatsink</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3 of each for X steppers, and 2 of each for Y steppers</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JST XH Series Connector</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>For wiring heaters and fans.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M1.6 Threaded Heat Insert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2 Threaded Heat Insert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2x3x4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nema17 40mm TR8x1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Commonly found TR8x2 would work, but 1mm thread pitch helps with layer stacking quality.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RTV Silicone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Temp resistant to 300℃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5mL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stepper Motor</t>
+  </si>
+  <si>
+    <t>CSE14RA1L410A-01</t>
+  </si>
+  <si>
+    <t>Moon's Nema14 Pancake 10T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Must be 10T.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Extruder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Toolhead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hotend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TZ-E3 2.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K1 all metal extruder gear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K1 all metal reduction gear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lubrication Grease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PTFE Grease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mobilux EP2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>For lubricating linear rails.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>For lubricating lead screws and extruder gears.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Double bearing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Comes in pairs, only need one. Must be double bearing variant, see image on the right.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Uses ~800mm for Y axis and ~550mm for X.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hotend Extender</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thermistor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Generic 3950 Thermistor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glass bead, 1.2mm diameter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4 of them are for belt tensioner.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>For hotend double shear. Stainless steel ones are preferred due to low heat conduction.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>304 stainless steel, 8mm thickness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ceramic Heater 7mm*35mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7~8Ω</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thermal Paste</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Temp resistant to 350℃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2mL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PTFE Tube</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ABEC7/P4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Miniature Bearing MR63ZZ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ABEC7/P4 or better recommended. Replaces the low quality one from K1 reduction gear.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Miniature Bearing 693ZZ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ABEC7/P4 or better recommended. Add to the front of the extruder gear for extra stability.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>U Groove Bearing U624ZZ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5mm wide*0.5mm deep groove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.8mm ID * 2.6mm OD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Smaller diameter tubes constrain the filament better.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stainless Steel Pin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3mm*14mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3mm*20mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4mm*10mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hotend Cooling Fan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3015 Fan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24V 12000RPM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Higher the CFM the better. At least 5CFM.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spring</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sherpa Mini Spring</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7mm Wire Width*5mm OD*15mm Length</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M1.6x2.5x5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Belt Clip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Screws (Body)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Screws (Ebox)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FHCS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M4x8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3x10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3x35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BHCS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHCS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3x6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Screw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2x35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3x14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3x20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M6x12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M6x30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M1.6x12 TC4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3x8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3x12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3x22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3x25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3x30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3x50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3x60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M4x16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M5x30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Small Head Screw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3x16, head diameter 4.5mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ultra Low Head Socket Cap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M4x14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magnetic Sheet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2mm Magnetic Sheet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Extra strong, 120mm*120mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Paste eaters are the most oppressed group in society. Replaces the godawful GD900 that comes with TZE3.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Electronics</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power Supply</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakout Board</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16AWG, Black</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16AWG, Red</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16AWG, Green+Yellow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Neutral/-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Live/24V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wire Splicing Connector</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wago 221-413</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LRS-350-24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LRS-150-48</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Board</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MT7601</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WiFi Dongle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fly-C8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD Card</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32GB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TMC2209</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stepper Driver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TMC5160</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOSFET Board</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10A peak</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The board's default fan ports can't keep up with 2.8A server fans.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ebox Cooling Fan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GND</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oops. Doesn't have enough clearance for regular screws on the toolhead unless you switch to LDO pancake motor and lose torque.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3x5x4 ("Voron Style")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4 extra for Y belt tensioner.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consider getting 2 of them to minimize downtime between prints.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Optional.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power Socket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AC-17 IEC320 C14 Electrical AC Power Socket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>With top and bottom screw holes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bimetal Nozzle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bimetal Volcano Nozzle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Surface Mounted 0805 Size</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Generic 3950 100K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Insulated wire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Silicone wire 4 Strand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>For bed heater and thermistor.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dish Soap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>For making custom RTV silicone socks. Rinse the mold with dish soap water.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self Tapping</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lower than 1.2mm head height, so it can sink below the magnetic sheet.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Due to the geometry of the 4.0mm width heavy duty 3060 extrusion, only 2020 nuts can fit in. Use NoDrop nuts provided to hold them in place during assembly. If using normal 3060 extrusion, get 3030 ones.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2x8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>For endstops.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M8x60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Must be in titanium TC4 for low conductivity. For hotend double shear.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M8x40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M8x100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M6x40</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -366,7 +1198,7 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FFFF3399"/>
+        <color theme="7" tint="-0.249977111117893"/>
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
@@ -393,11 +1225,109 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PEI Sheet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Voron 0 Textured PEI</t>
+    <r>
+      <t xml:space="preserve">3060 extrusion (3mm thickness) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Custom ordered)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Steel Plate</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Custom ordered)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>35mm Super Extender</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Custom ordered)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">X Axis Belt Clip </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Custom ordered)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Carbon Fiber Sheet</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF3399"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Custom ordered)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1mm Aluminum PCB</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Custom ordered)</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -408,7 +1338,7 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FFFF3399"/>
+        <color theme="7" tint="-0.249977111117893"/>
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
@@ -427,610 +1357,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Cooling</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cooling Fan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weaker variants would work.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GFC0412DS-SM06</t>
-  </si>
-  <si>
-    <t>Misc.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Endstops</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D2F style microswitch</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>No lever</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Microbreak board </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF3399"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Custom ordered)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nut</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CLS-M6-00 (304 stainless steel, thinnest variant)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>200g</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pack PET parts tightly in salt and air fry for 2 hours at 130-140C.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>T nut</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2020 M3 Nut</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nuts</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2020 M5 Nut</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Popcorn Salt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Delta 4056 Fan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Integrated Lead Screw Stepper</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90 Degree 3030 Corner Bracket</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Threaded Heat Insert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dimensions are in hole diameter x outer diameter x height.
-Some vendors use hole diameter x height x outer diameter, check before buying.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Self-Clinching Nut</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M6x8x10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M6 Threaded Heat Insert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3 Threaded Heat Insert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3x5x10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3 Nut</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M4 Nut</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M6 Nut</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Due to the geometry of the 3.0mm 3060 extrusion, only 2020 nuts can fit in. Use NoDrop nuts provided to hold them in place during assembly. If using normal 3060 extrusion, get 3030 ones.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Shim</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3 Shim</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3x16x1, stainless steel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10mm~16mm diameter ones would work. Grind the top surface on the extrusion away, and put the sharp side of the shim towards the extrusion to ground the frame.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wire</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26AWG</t>
-  </si>
-  <si>
-    <t>26AWG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15m</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5m</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Silicone wire</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20AWG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wire Sleeve</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Split Braided Sleeving</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6mm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2m</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>For wiring thermistors and endstops.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Micro-Fit 3.0 Crimp Terminal, Female</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Crimp Terminal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wiring</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Micro-Fit 3.0 Receptacle Housing, Dual Row</t>
-  </si>
-  <si>
-    <t>430252400 (2x12)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wire Housing</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>430252000 (2x10)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Uses 43. Buy extra if not confident with wiring.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buy extra if not confident with wiring.</t>
-  </si>
-  <si>
-    <t>Micro-Fit 3.0 Receptacle Housing, Dual Row</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Micro-Fit 3.0 Vertical Header, Dual Row</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>430452412 (2x12)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>430452012 (2x10)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wire Connector</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Use expensive ones for Z axis. Can use cheap ones for X and Y.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>JST XH Series Straight Through Hole PCB Header</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2 Pin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Screw Terminal Block</t>
-  </si>
-  <si>
-    <t>2pin, 3.5mm pitch</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Both top entry and side entry would work.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3 Pin</t>
-  </si>
-  <si>
-    <t>4 Pin</t>
-  </si>
-  <si>
-    <t>425 Glue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>407 Glue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Basically plastic-safe threadlocker. Apply on screws after installing.
-Warning: if accidentally went into screw socket, immediately insert screwdriver into socket and wait 30 seconds for it to dry to prevent gluing the socket shut.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Glue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>30x40x5mm</t>
-  </si>
-  <si>
-    <t>Heatsink</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3 of each for X steppers, and 2 of each for Y steppers</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>JST XH Series Connector</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>600mm for toolhead and 1.2m for harness.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>For wiring heaters and fans.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M1.6 Threaded Heat Insert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M2 Threaded Heat Insert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M2x3x4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nema17 40mm TR8x1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Commonly found TR8x2 would work, but 1mm thread pitch helps with layer stacking quality.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RTV Silicone</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Temp resistant to 300℃</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5mL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stepper Motor</t>
-  </si>
-  <si>
-    <t>CSE14RA1L410A-01</t>
-  </si>
-  <si>
-    <t>Moon's Nema14 Pancake 10T</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Must be 10T.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Extruder</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Toolhead</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hotend</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TZ-E3 2.0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>K1 all metal extruder gear</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>K1 all metal reduction gear</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lubrication Grease</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PTFE Grease</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mobilux EP2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>For lubricating linear rails.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>For lubricating lead screws and extruder gears.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Double bearing</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Comes in pairs, only need one. Must be double bearing variant, see image on the right.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Uses ~800mm for Y axis and ~550mm for X.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hotend Extender</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Thermistor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Generic 3950 Thermistor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>35mm Super Extender</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF3399"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Custom ordered)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>glass bead, 1.2mm diameter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4 of them are for belt tensioner.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>For hotend double shear. Stainless steel ones are preferred due to low heat conduction.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>304 stainless steel, 8mm thickness</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ceramic Heater 7mm*35mm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7~8Ω</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Thermal Paste</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Temp resistant to 350℃</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2mL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PTFE Tube</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ABEC7/P4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Miniature Bearing MR63ZZ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ABEC7/P4 or better recommended. Replaces the low quality one from K1 reduction gear.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Miniature Bearing 693ZZ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ABEC7/P4 or better recommended. Add to the front of the extruder gear for extra stability.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>U Groove Bearing U624ZZ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.5mm wide*0.5mm deep groove</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.8mm ID * 2.6mm OD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Smaller diameter tubes constrain the filament better.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stainless Steel Pin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3mm*14mm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3mm*20mm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4mm*10mm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hotend Cooling Fan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3015 Fan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>24V 12000RPM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Higher the CFM the better. At least 5CFM.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Spring</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sherpa Mini Spring</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.7mm Wire Width*5mm OD*15mm Length</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M1.6x2.5x5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Belt Clip</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">X Axis Belt Clip </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF3399"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Custom ordered)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Check </t>
     </r>
@@ -1038,7 +1364,7 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FFFF3399"/>
+        <color theme="7" tint="-0.249977111117893"/>
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
@@ -1057,371 +1383,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Screws (Body)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Screws (Ebox)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FHCS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M4x8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3x10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3x35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BHCS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SHCS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3x6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Screw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M2x35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3x14</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3x20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M6x12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M6x30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M6x50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M8x35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M8x90</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Must be in titanium TC4 for hotend double shear.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M1.6x12 TC4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3x8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3x12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3x22</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3x25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3x30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3x50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3x60</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M4x16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M5x30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Small Head Screw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3x16, head diameter 4.5mm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ultra Low Head Socket Cap</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M4x14</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Magnetic Sheet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2mm Magnetic Sheet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Extra strong, 120mm*120mm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Paste eaters are the most oppressed group in society. Replaces the godawful GD900 that comes with TZE3.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Electronics</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Power Supply</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Breakout Board</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16AWG, Black</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16AWG, Red</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16AWG, Green+Yellow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1m</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Neutral/-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Live/24V</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wire Splicing Connector</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wago 221-413</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LRS-350-24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LRS-150-48</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Board</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MT7601</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WiFi Dongle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fly-C8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SD Card</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>32GB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TMC2209</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stepper Driver</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Z axis.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E axis.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TMC2240</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TMC5160</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MOSFET Board</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10A peak</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>The board's default fan ports can't keep up with 2.8A server fans.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ebox Cooling Fan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GND</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Oops. Doesn't have enough clearance for regular screws on the toolhead unless you switch to LDO pancake motor and lose torque.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M3x5x4 ("Voron Style")</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4 extra for Y belt tensioner.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Consider getting 2 of them to minimize downtime between prints.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Optional.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Power Socket</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AC-17 IEC320 C14 Electrical AC Power Socket</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>With top and bottom screw holes</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fly-C8 doesn't support the addon WiFi module if you don't use the bloat filled system image. Flawless design.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bimetal Nozzle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bimetal Volcano Nozzle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Surface Mounted 0805 Size</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Generic 3950 100K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8m</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Insulated wire</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Silicone wire 4 Strand</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>230mm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>For bed heater and thermistor.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dish Soap</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>For making custom RTV silicone socks. Rinse the mold with dish soap water.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Self Tapping</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M2x10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>For X and Y endstops.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lower than 1.2mm head height, so it can sink below the magnetic sheet.</t>
+    <r>
+      <t xml:space="preserve">"Microbreak" breakout board </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Custom ordered)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fly-C8 doesn't support the addon WiFi module if you don't use the bloat filled default image. Flawless design.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z and E axis.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>260mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>600mm for toolhead and 1m for harness.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1429,7 +1419,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1463,8 +1453,15 @@
       <name val="等线"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1483,6 +1480,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1496,7 +1499,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1539,6 +1542,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1883,7 +1895,7 @@
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="19.21875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="44.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50" style="1" customWidth="1"/>
     <col min="3" max="3" width="43.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.88671875" style="7" customWidth="1"/>
     <col min="5" max="5" width="83.33203125" style="4" customWidth="1"/>
@@ -1891,19 +1903,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:5">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="17" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1981,7 +1993,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>291</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>27</v>
@@ -1989,8 +2001,8 @@
       <c r="D9" s="7">
         <v>2</v>
       </c>
-      <c r="E9" s="15" t="s">
-        <v>65</v>
+      <c r="E9" s="18" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1998,7 +2010,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>291</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
@@ -2006,14 +2018,14 @@
       <c r="D10" s="7">
         <v>1</v>
       </c>
-      <c r="E10" s="15"/>
+      <c r="E10" s="18"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>291</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -2021,48 +2033,48 @@
       <c r="D11" s="7">
         <v>1</v>
       </c>
-      <c r="E11" s="15"/>
+      <c r="E11" s="18"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>292</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D12" s="7">
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D13" s="7">
         <v>2</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D14" s="7">
         <v>4</v>
@@ -2091,7 +2103,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2107,7 +2119,7 @@
       <c r="D18" s="7">
         <v>4</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="18" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2124,34 +2136,34 @@
       <c r="D19" s="7">
         <v>2</v>
       </c>
-      <c r="E19" s="15"/>
+      <c r="E19" s="18"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="D20" s="7">
         <v>2</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D21" s="7">
         <v>2</v>
@@ -2159,13 +2171,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="C22" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D22" s="7">
         <v>4</v>
@@ -2173,41 +2185,41 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D23" s="7">
         <v>2</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D24" s="7">
         <v>14</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -2216,44 +2228,44 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D27" s="7">
         <v>1</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D28" s="7">
         <v>1</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D29" s="7">
         <v>1</v>
@@ -2261,10 +2273,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="D30" s="7">
         <v>1</v>
@@ -2272,24 +2284,24 @@
     </row>
     <row r="31" spans="1:5" ht="27.6">
       <c r="A31" s="1" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>178</v>
+        <v>293</v>
       </c>
       <c r="D31" s="7">
         <v>1</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>213</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>212</v>
+        <v>294</v>
       </c>
       <c r="D32" s="7">
         <v>2</v>
@@ -2297,13 +2309,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="D33" s="7">
         <v>1</v>
@@ -2311,13 +2323,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D34" s="7">
         <v>1</v>
@@ -2328,16 +2340,16 @@
         <v>23</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="D35" s="7">
         <v>1</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2345,16 +2357,16 @@
         <v>23</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="D36" s="7">
         <v>1</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2362,10 +2374,10 @@
         <v>23</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="D37" s="7">
         <v>1</v>
@@ -2373,30 +2385,30 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="D38" s="7">
         <v>1</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="D39" s="7">
         <v>1</v>
@@ -2404,13 +2416,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="D40" s="7">
         <v>1</v>
@@ -2418,13 +2430,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D41" s="7">
         <v>1</v>
@@ -2432,30 +2444,30 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="D42" s="7">
         <v>1</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="D43" s="7">
         <v>1</v>
@@ -2463,10 +2475,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="D44" s="7">
         <v>1</v>
@@ -2474,7 +2486,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -2483,56 +2495,56 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D47" s="7">
         <v>1</v>
       </c>
-      <c r="E47" s="15" t="s">
-        <v>54</v>
+      <c r="E47" s="18" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="C48" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D48" s="7">
         <v>2</v>
       </c>
-      <c r="E48" s="15"/>
+      <c r="E48" s="18"/>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D49" s="7">
         <v>2</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -2541,42 +2553,42 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>62</v>
+        <v>295</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D52" s="7">
         <v>1</v>
       </c>
-      <c r="E52" s="15" t="s">
-        <v>68</v>
+      <c r="E52" s="18" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>64</v>
+        <v>296</v>
       </c>
       <c r="D53" s="7">
         <v>1</v>
       </c>
-      <c r="E53" s="15"/>
+      <c r="E53" s="18"/>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="D54" s="7">
         <v>1</v>
@@ -2584,38 +2596,38 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="1" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="D55" s="7">
         <v>1</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D56" s="7">
         <v>1</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -2624,24 +2636,24 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D59" s="7">
         <v>3</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -2650,38 +2662,38 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="41.4">
       <c r="A63" s="1" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D63" s="7">
         <v>1</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="1" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D64" s="7">
         <v>1</v>
@@ -2689,13 +2701,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D65" s="7">
         <v>1</v>
@@ -2703,61 +2715,61 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="1" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="27.6">
       <c r="A69" s="1" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -2775,7 +2787,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6375C457-B0C0-4589-A3C9-93DBFBDBB730}">
-  <dimension ref="A2:E47"/>
+  <dimension ref="A2:E46"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="41.77734375" style="1" customWidth="1"/>
@@ -2805,7 +2817,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="6" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="13"/>
@@ -2814,10 +2826,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="D4" s="7">
         <v>1</v>
@@ -2825,10 +2837,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="D5" s="7">
         <v>1</v>
@@ -2836,10 +2848,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="D6" s="7">
         <v>1</v>
@@ -2847,30 +2859,30 @@
     </row>
     <row r="7" spans="1:5" ht="27.6">
       <c r="A7" s="1" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="D7" s="7">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="D8" s="7">
         <v>1</v>
@@ -2878,104 +2890,101 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="D9" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="D10" s="7">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>273</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="D11" s="7">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>278</v>
-      </c>
+      <c r="B12"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="B13"/>
+      <c r="A13" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="3"/>
+      <c r="A14" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>77</v>
+        <v>121</v>
+      </c>
+      <c r="B15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="D15" s="7">
         <v>1</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B16" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D16" s="7">
         <v>1</v>
@@ -2983,411 +2992,397 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B17" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D17" s="7">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B18" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D18" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B19" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D19" s="7">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B20" t="s">
-        <v>134</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D20" s="7">
-        <v>3</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>136</v>
-      </c>
+      <c r="B20"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="B21"/>
+      <c r="A21" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="3"/>
+      <c r="A22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="7">
+        <v>50</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="7">
-        <v>50</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>124</v>
+        <v>275</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B24" t="s">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B25" t="s">
-        <v>296</v>
+        <v>117</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>108</v>
+        <v>112</v>
+      </c>
+      <c r="D25" s="7">
+        <v>1</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D26" s="7">
         <v>1</v>
       </c>
-      <c r="E26" s="15" t="s">
-        <v>125</v>
-      </c>
+      <c r="E26" s="18"/>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D27" s="7">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15"/>
+        <v>12</v>
+      </c>
+      <c r="E27" s="18"/>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B28" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D28" s="7">
-        <v>12</v>
-      </c>
-      <c r="E28" s="15"/>
+        <v>9</v>
+      </c>
+      <c r="E28" s="18"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B29" t="s">
-        <v>146</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="D29" s="7">
-        <v>9</v>
-      </c>
-      <c r="E29" s="15"/>
+      <c r="B29"/>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" spans="1:5">
       <c r="B30"/>
-      <c r="E30" s="10"/>
     </row>
     <row r="31" spans="1:5">
-      <c r="B31"/>
+      <c r="A31" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="3"/>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="3"/>
+      <c r="A32" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" s="7">
+        <v>12</v>
+      </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B33" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D33" s="7">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B34" t="s">
-        <v>146</v>
+        <v>96</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="D34" s="7">
-        <v>4</v>
+        <v>98</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>109</v>
+        <v>274</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>111</v>
+        <v>237</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>295</v>
+        <v>240</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>148</v>
+        <v>241</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>110</v>
+        <v>276</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>256</v>
+        <v>102</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>257</v>
+        <v>302</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
-        <v>105</v>
+        <v>243</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="D41" s="7">
+        <v>244</v>
+      </c>
+      <c r="D40" s="7">
         <v>4</v>
       </c>
     </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="3"/>
+    </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="3"/>
+      <c r="A43" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D43" s="7">
+        <v>4</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D44" s="7">
-        <v>4</v>
+        <v>105</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>106</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>131</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1" t="s">
-        <v>112</v>
+        <v>259</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>147</v>
+        <v>260</v>
+      </c>
+      <c r="C45" s="11">
+        <v>9225</v>
+      </c>
+      <c r="D45" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C46" s="11">
-        <v>9225</v>
+        <v>268</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>269</v>
       </c>
       <c r="D46" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="D47" s="7">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="E26:E29"/>
+    <mergeCell ref="E25:E28"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3396,7 +3391,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D94751F-96BF-42B2-B88F-498F6EAA5B76}">
-  <dimension ref="A2:E50"/>
+  <dimension ref="A2:E51"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="19.21875" style="1" customWidth="1"/>
@@ -3426,7 +3421,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="6" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3435,30 +3430,30 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="D4" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="D5" s="7">
         <v>2</v>
@@ -3466,13 +3461,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="D6" s="7">
         <v>4</v>
@@ -3480,13 +3475,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D7" s="7">
         <v>4</v>
@@ -3494,13 +3489,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="D8" s="7">
         <v>5</v>
@@ -3508,13 +3503,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="D9" s="7">
         <v>4</v>
@@ -3522,44 +3517,44 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D10" s="7">
         <v>12</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D11" s="7">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>229</v>
+        <v>289</v>
       </c>
       <c r="D12" s="7">
         <v>2</v>
@@ -3567,120 +3562,120 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>230</v>
+        <v>287</v>
       </c>
       <c r="D13" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>231</v>
+        <v>285</v>
       </c>
       <c r="D14" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="27.6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="D15" s="7">
         <v>2</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+    </row>
+    <row r="16" spans="1:5" ht="27.6">
       <c r="A16" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="D16" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>305</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D17" s="7">
         <v>4</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>232</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="D18" s="7">
         <v>4</v>
       </c>
+      <c r="E18" s="4" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D19" s="7">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="D20" s="7">
         <v>29</v>
@@ -3688,148 +3683,148 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="D21" s="7">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="D22" s="7">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="D23" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="D24" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="D25" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="D26" s="7">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="D27" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="D28" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D29" s="7">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="3"/>
-    </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D31" s="7">
-        <v>4</v>
-      </c>
+      <c r="A31" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="3"/>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="D32" s="7">
         <v>4</v>
@@ -3837,226 +3832,240 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="D33" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="D34" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D35" s="7">
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="3"/>
-    </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D37" s="7">
-        <v>2</v>
-      </c>
+      <c r="A37" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="3"/>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D38" s="7">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D39" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D40" s="7">
-        <v>1</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="13.8" customHeight="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D41" s="7">
+        <v>1</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="13.8" customHeight="1">
+      <c r="A42" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42" s="7">
+        <v>32</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" s="7">
+        <v>8</v>
+      </c>
+      <c r="E43" s="18"/>
+    </row>
+    <row r="44" spans="1:5" ht="13.8" customHeight="1">
+      <c r="A44" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B44" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D44" s="7">
+        <v>4</v>
+      </c>
+      <c r="E44" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="D41" s="7">
-        <v>32</v>
-      </c>
-      <c r="E41" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="1" t="s">
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D42" s="7">
-        <v>8</v>
-      </c>
-      <c r="E42" s="15"/>
-    </row>
-    <row r="43" spans="1:5" ht="13.8" customHeight="1">
-      <c r="A43" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D43" s="7">
-        <v>4</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D44" s="7">
+      <c r="B45" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D45" s="7">
         <v>2</v>
       </c>
-      <c r="E44" s="15"/>
-    </row>
-    <row r="45" spans="1:5" ht="13.8" customHeight="1">
-      <c r="A45" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="D45" s="7">
+      <c r="E45" s="18"/>
+    </row>
+    <row r="46" spans="1:5" ht="13.8" customHeight="1">
+      <c r="A46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D46" s="7">
         <v>44</v>
       </c>
-      <c r="E45" s="15"/>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D46" s="7">
-        <v>12</v>
-      </c>
-      <c r="E46" s="15"/>
+      <c r="E46" s="18"/>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47" s="7">
+        <v>12</v>
+      </c>
+      <c r="E47" s="18"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D48" s="7">
+        <v>6</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="3"/>
+    </row>
+    <row r="51" spans="1:5" ht="27.6">
+      <c r="A51" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D47" s="7">
-        <v>6</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="3"/>
-    </row>
-    <row r="50" spans="1:5" ht="27.6">
-      <c r="A50" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D50" s="7">
+      <c r="D51" s="7">
         <v>2</v>
       </c>
-      <c r="E50" s="4" t="s">
-        <v>104</v>
+      <c r="E51" s="4" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="E43:E46"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="E44:E47"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
